--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_300_Greece_without_Crete.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_300_Greece_without_Crete.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R7e029529896d44e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R44692a75502f487f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra6bbb056162a46fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc7835e4ef1de4fc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd22931f2d28d4e0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re5d450a95da5445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R827785bce44a411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9fa73db12ea942d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0c790c5ad1434e52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R0a7e0c087a674dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R027c40f1c5264c54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R427ffe9fd3b84e26"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ300CommercialTable" displayName="EEZ300CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ300CommercialTable" displayName="EEZ300CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ300FunctionalTable" displayName="EEZ300FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ300FunctionalTable" displayName="EEZ300FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ300ValidationTable" displayName="EEZ300ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ300ValidationTable" displayName="EEZ300ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -11079,7 +11033,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63a0d53424314d81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabbf4ce6fc714f74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11089,20 +11043,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11110,714 +11054,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>16442.7546809864</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>16442.7546809864</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$156,A2,'Species'!$U$2:$U$156))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2118237.1346380906</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>2118237.1346380906</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1184.4162503844998</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.159211368638668</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1442.8173916381372</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1184.4162503844998</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1468.5940665439446</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$156,A3,'Species'!$U$2:$U$156))</x:f>
-        <x:v>1739426.6776329034</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.159211368638668</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1442.8173916381372</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1708896.364993587</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>30530.312639316544</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0178655144131172</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.017865514413117217</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>9544.5613152254</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.31485194484741</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>206.46761679189345</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>9544.5613152254</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>233.68807929260524</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$156,A4,'Species'!$U$2:$U$156))</x:f>
-        <x:v>2230450.201445526</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.31485194484741</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>206.46761679189345</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1970642.8280786886</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>259807.3733668374</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1318388952401592</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.13183889524015927</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>982.8729502663</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3514404561361077</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>224.61587956970564</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>982.8729502663</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>452.9675529615338</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$156,A5,'Species'!$U$2:$U$156))</x:f>
-        <x:v>445209.5551542092</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3514404561361077</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>224.61587956970564</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>220768.87222933653</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>224440.68292487267</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.01663192214762</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.0166319221476199</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>16816.7082089033</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.100509534290573</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>126.0403307874058</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>16816.7082089033</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>131.07202064825344</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$156,A6,'Species'!$U$2:$U$156))</x:f>
-        <x:v>2204199.9255930264</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.100509534290573</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>126.0403307874058</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2119583.4654054544</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>84616.46018757205</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.039921268290978</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03992126829097801</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.077416208</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.3066145321920186</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>20.258838026982986</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.077416208</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>34.59071191876467</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$156,A7,'Species'!$U$2:$U$156))</x:f>
-        <x:v>2.677881748771165</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.3066145321920186</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>20.258838026982986</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1.5683624185352245</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1.1095193302359403</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7074381004820163</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7074381004820163</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>22111.9650859973</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7235370044544265</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>529.0990776548132</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>22111.9650859973</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>790.8696269061879</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$156,A8,'Species'!$U$2:$U$156))</x:f>
-        <x:v>17487681.57772534</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7235370044544265</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>529.0990776548132</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>11699420.332136603</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>5788261.245588737</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4947476952930074</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4947476952930075</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>33533.736161906905</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.365794768407048</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>232.16394157199437</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>33533.736161906905</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>483.46046351469175</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$156,A9,'Species'!$U$2:$U$156))</x:f>
-        <x:v>16212235.628214892</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.365794768407048</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>232.16394157199437</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>7785324.362983629</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>8426911.265231263</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.0824097844012956</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.0824097844012954</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.009114748</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.35</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>223.872113856834</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.009114748</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$156,A10,'Species'!$U$2:$U$156))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2.04053790203235</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>2.04053790203235</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>827.5097966296001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8643260068556007</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>731.6881253157524</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>827.5097966296001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>745.2702115318078</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$156,A11,'Species'!$U$2:$U$156))</x:f>
-        <x:v>616718.4011787854</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8643260068556007</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>731.6881253157524</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>605479.0917763317</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>11239.309402453713</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0185626713706666</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.018562671370666577</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>616.5828886247999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.8801760172499224</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>758.8850848085135</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>616.5828886247999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>846.5578379735541</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$156,A12,'Species'!$U$2:$U$156))</x:f>
-        <x:v>521973.0771256993</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.8801760172499224</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>758.8850848085135</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>467915.5577255095</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>54057.519400189805</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1155283651241648</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.11552836512416466</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>6455.570643023299</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.407704552891124</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2556.8458930365928</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>6455.570643023299</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2648.370710000409</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$156,A13,'Species'!$U$2:$U$156))</x:f>
-        <x:v>17096744.207321413</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.407704552891124</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2556.8458930365928</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>16505899.28582172</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>590844.9214996938</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0357959848941536</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.035795984894153525</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5e9633c5c6a44a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R587ba87423564bf6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11827,20 +11307,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11848,1416 +11318,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>9340.839684412198</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.918777006031291</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>829.4247795653304</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>9340.839684412198</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1020.6225393676157</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$156,A2,'Species'!$U$2:$U$156))</x:f>
-        <x:v>9533471.518530576</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.918777006031291</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>829.4247795653304</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>7747523.896198678</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1785947.6223318977</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.2305185045260942</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.23051850452609418</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>61.9654402786</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.1377329018804945</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1373.1971768182796</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>61.9654402786</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1375.7150088848186</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$156,A3,'Species'!$U$2:$U$156))</x:f>
-        <x:v>85246.7862234259</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.1377329018804945</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1373.1971768182796</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>85090.76765087522</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>156.01857255067443</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0018335546482646</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0018335546482647071</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>472.10899044079997</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.52947554884528</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>3384.352171346592</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>472.10899044079997</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>3387.606666973616</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$156,A4,'Species'!$U$2:$U$156))</x:f>
-        <x:v>1599319.5635554371</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.52947554884528</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>3384.352171346592</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1597783.0869105689</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1536.476644868264</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.000961630309806</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0009616303098057914</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>834.6267615787001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.827841539918039</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>672.731153547855</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>834.6267615787001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>720.3069836039537</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$156,A5,'Species'!$U$2:$U$156))</x:f>
-        <x:v>601187.4850678897</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.827841539918039</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>672.731153547855</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>561479.4240987494</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>39708.060969140264</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.070720420490701</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.07072042049070112</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>137.2390443006</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>137.2390443006</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$156,A6,'Species'!$U$2:$U$156))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>314396.4872850082</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>314396.4872850082</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5080.135003932999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.441237735180737</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2762.089425358637</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5080.135003932999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2818.6637769460867</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$156,A7,'Species'!$U$2:$U$156))</x:f>
-        <x:v>14319192.51758181</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.441237735180737</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2762.089425358637</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>14031787.173757594</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>287405.34382421523</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.020482447479087</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.020482447479086906</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>95.2570461647</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.8401568600982143</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>692.0808941366589</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>95.2570461647</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>692.46807527056</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$156,A8,'Species'!$U$2:$U$156))</x:f>
-        <x:v>65962.46341362869</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.8401568600982143</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>692.0808941366589</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>65925.58168248257</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>36.88173114611709</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.000559444910532</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0005594449105318569</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1468.2308483232</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.268308357040566</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1854.8481321506251</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1468.2308483232</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2217.4549200589827</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$156,A9,'Species'!$U$2:$U$156))</x:f>
-        <x:v>3255735.718396654</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.268308357040566</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1854.8481321506251</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2723345.246578215</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>532390.4718184387</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.195491362135362</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.19549136213536206</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>304.944369895</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9495994065822684</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>890.4292269150249</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>304.944369895</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1047.6960026210668</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$156,A10,'Species'!$U$2:$U$156))</x:f>
-        <x:v>319488.9973607915</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9495994065822684</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>890.4292269150249</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>271531.3795376943</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>47957.617823097215</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1766190629780957</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.17661906297809565</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>8252.8416294119</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.4083941567553633</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>256.0909060999881</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>8252.8416294119</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>261.7426372275143</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$156,A11,'Species'!$U$2:$U$156))</x:f>
-        <x:v>2160120.532703287</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.4083941567553633</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>256.0909060999881</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2113477.690775796</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>46642.84192749113</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0220692378874223</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.022069237887422367</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>922.9665544259</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.456343642119867</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2859.8525501977974</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>922.9665544259</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2873.9505246697086</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$156,A12,'Species'!$U$2:$U$156))</x:f>
-        <x:v>2652560.2133449083</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.456343642119867</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2859.8525501977974</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2639548.254422184</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>13011.95892272424</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0049296158541237</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.004929615854123739</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.007583376</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.007583376</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$156,A13,'Species'!$U$2:$U$156))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>9.11722325913126</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>9.11722325913126</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>6374.374482941699</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.583700624431164</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>383.44283275905906</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>6374.374482941699</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>677.40038900514</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$156,A14,'Species'!$U$2:$U$156))</x:f>
-        <x:v>4318003.754409146</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.583700624431164</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>383.44283275905906</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>2444208.2088062274</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1873795.5456029181</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.7666268114360422</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.7666268114360422</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>23271.073560735796</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.311994653233242</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>205.11369263328442</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>23271.073560735796</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>274.4698323502313</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$156,A15,'Species'!$U$2:$U$156))</x:f>
-        <x:v>6387207.658825054</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.311994653233242</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>205.11369263328442</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>4773215.829583313</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1613991.8292417405</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.33813510364199</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.3381351036419899</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>5875.954519959501</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.981200048070666</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>957.6350829668247</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>5875.954519959501</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1283.2804532391533</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$156,A16,'Species'!$U$2:$U$156))</x:f>
-        <x:v>7540497.5795862805</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.981200048070666</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>957.6350829668247</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>5627020.1942307055</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1913477.385355575</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.3400516293361509</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.3400516293361508</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>3098.6131930824</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.567532925250705</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>36.94306510133081</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>3098.6131930824</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>52.73355355279315</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$156,A17,'Species'!$U$2:$U$156))</x:f>
-        <x:v>163400.88475680212</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.567532925250705</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>36.94306510133081</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>114472.26891588564</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>48928.61584091648</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.4274276757532367</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.42742767575323665</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>23.828263794999998</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0010068383792627</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.02321020450468</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>23.828263794999998</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>10.080247365029171</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$156,A18,'Species'!$U$2:$U$156))</x:f>
-        <x:v>240.1947933327687</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0010068383792627</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.02321020450468</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>238.8356968256734</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>1.3590965070953018</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0056905082663892</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.005690508266389126</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>1291.7196858135</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.7172075263100877</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>52.14438219416411</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>1291.7196858135</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>54.44654092884441</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$156,A19,'Species'!$U$2:$U$156))</x:f>
-        <x:v>70329.66874223878</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.7172075263100877</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>52.14438219416411</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>67355.92498478472</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>2973.7437574540527</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0441496981613094</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.04414969816130953</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>2816.4181098182</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.5399733058626452</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>346.7155387457385</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>2816.4181098182</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>360.86774389454337</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$156,A20,'Species'!$U$2:$U$156))</x:f>
-        <x:v>1016354.449153828</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.5399733058626452</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>346.7155387457385</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>976495.9222788716</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>39858.526874956326</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0408179143052</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.040817914305200105</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>3266.3293895478996</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.3368801704787825</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>217.21017749153555</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>3266.3293895478996</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>323.6396116862023</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$156,A21,'Species'!$U$2:$U$156))</x:f>
-        <x:v>1057113.5752725124</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.3368801704787825</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>217.21017749153555</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>709479.9864495182</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>347633.58882299415</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.489983643601664</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.489983643601664</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>33259.5732937987</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.1052017286920517</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>127.40947573929347</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>33259.5732937987</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>129.96121507299748</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$156,A22,'Species'!$U$2:$U$156))</x:f>
-        <x:v>4322454.558071496</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.1052017286920517</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>127.40947573929347</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>4237584.796675499</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>84869.76139599737</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0200278614985074</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.02002786149850736</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>1205.7016783397</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.699455186394353</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>500.55889862254344</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>1205.7016783397</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>516.9211481814904</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$156,A23,'Species'!$U$2:$U$156))</x:f>
-        <x:v>623252.6959317077</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.699455186394353</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>500.55889862254344</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>603524.7041770724</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>19727.991754635354</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0326879606055814</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.03268796060558147</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>845.6339059656999</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.187759994716975</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>154.08486944164073</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>845.6339059656999</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>154.69231655253304</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$156,A24,'Species'!$U$2:$U$156))</x:f>
-        <x:v>130813.06786920101</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.187759994716975</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>154.08486944164073</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>130299.38999614956</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>513.6778730514488</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0039422891624177</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.003942289162417632</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>216.31200475010002</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.7999383641184066</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>630.8678041929395</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>216.31200475010002</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>630.8949316450521</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$156,A25,'Species'!$U$2:$U$156))</x:f>
-        <x:v>136470.14745081853</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.7999383641184066</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>630.8678041929395</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>136464.2794572683</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>5.867993550229585</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0000430002164198</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.000043000216419763216</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>0.069467815</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.8543020159767516</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>714.9933721215124</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>0.069467815</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>740.9028261590279</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$156,A26,'Species'!$U$2:$U$156))</x:f>
-        <x:v>51.46890046059251</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.8543020159767516</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>714.9933721215124</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>49.66902730076338</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>1.7998731598291258</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0362373345652667</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.03623733456526665</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e10f9a8e94d4a72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d39503b162f4a04"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13432,7 +11983,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -13531,7 +12082,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>60672881.10444954</x:v>
+        <x:v>45202170.90468926</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13545,7 +12096,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>60672881.10444955</x:v>
+        <x:v>51972308.116400525</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13559,7 +12110,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-15470710.199760288</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13573,7 +12124,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-8700572.988049023</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13584,9 +12135,9 @@
         <x:v>EEZ_300</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13598,47 +12149,19 @@
         <x:v>EEZ_300</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_300</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_300</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9afa28beca4a4691"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0809ae91fcb4b89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13685,7 +12208,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
